--- a/Ejecucion_Pruebas.xlsx
+++ b/Ejecucion_Pruebas.xlsx
@@ -18,15 +18,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="217">
+  <si>
+    <t>RF</t>
+  </si>
   <si>
     <t>ID Principal</t>
   </si>
   <si>
     <t>Estados recomendados</t>
-  </si>
-  <si>
-    <t>RF</t>
   </si>
   <si>
     <t>HU</t>
@@ -35,10 +35,10 @@
     <t>ID CP</t>
   </si>
   <si>
-    <t>Estado</t>
+    <t>Resultado Obtenido</t>
   </si>
   <si>
-    <t>Resultado Obtenido</t>
+    <t>Estado</t>
   </si>
   <si>
     <t>Significado</t>
@@ -59,37 +59,37 @@
     <t>Bug</t>
   </si>
   <si>
-    <t>Severidad</t>
-  </si>
-  <si>
     <t>FAIL</t>
   </si>
   <si>
     <t>La prueba falló</t>
   </si>
   <si>
-    <t>RF-002.1 Registrar Empleado</t>
+    <t>Severidad</t>
   </si>
   <si>
     <t>BLOCKED</t>
   </si>
   <si>
+    <t>No pudo ejecutarse</t>
+  </si>
+  <si>
+    <t>RF-002.1 Registrar Empleado</t>
+  </si>
+  <si>
+    <t>NOT EXECUTED</t>
+  </si>
+  <si>
     <t>HU-002.1 Registrar Empleado</t>
   </si>
   <si>
-    <t>No pudo ejecutarse</t>
+    <t>Aún no ejecutada</t>
   </si>
   <si>
     <t>CP-001</t>
   </si>
   <si>
     <t>El sistema registró correctamente el empleado y generó contraseña temporal.</t>
-  </si>
-  <si>
-    <t>NOT EXECUTED</t>
-  </si>
-  <si>
-    <t>Aún no ejecutada</t>
   </si>
   <si>
     <t>Captura_RegistroExitoso.png</t>
@@ -104,9 +104,6 @@
     <t>El sistema permitió registrar dos empleados con el mismo documento.</t>
   </si>
   <si>
-    <t>CP-RF-001</t>
-  </si>
-  <si>
     <t>Video_DocumentoDuplicado.mp4</t>
   </si>
   <si>
@@ -117,6 +114,9 @@
   </si>
   <si>
     <t>Alta</t>
+  </si>
+  <si>
+    <t>CP-RF-001</t>
   </si>
   <si>
     <t>CP-003</t>
@@ -137,9 +137,6 @@
     <t>El sistema permitió guardar sin diligenciar el campo correo.</t>
   </si>
   <si>
-    <t>CP-RF-002</t>
-  </si>
-  <si>
     <t>Captura_CamposVacios.png</t>
   </si>
   <si>
@@ -147,6 +144,9 @@
   </si>
   <si>
     <t>BUG-002</t>
+  </si>
+  <si>
+    <t>CP-RF-002</t>
   </si>
   <si>
     <t>CP-RF-003</t>
@@ -347,34 +347,172 @@
     <t>CP-RNF-009</t>
   </si>
   <si>
+    <t>El sistema borro el usuario y todos los servicios acociados a este</t>
+  </si>
+  <si>
+    <t>1. https://drive.google.com/file/d/1Wq3c8G2nYHdKpX7fTtt7_Nm6fOb3eYSA/view?usp=drive_link 2. https://drive.google.com/file/d/1fK0PohvPoQ-y9p5C-1lhUG5ZVB1E0lBn/view?usp=drive_link 3. https://drive.google.com/file/d/1W3_agnbpcJB7lV7Qi6jE5EoSDpf9Nc15/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Cumple con el borrado en cascada</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>RNF-010 Validaciones de negocio en el flujo de servicios</t>
+  </si>
+  <si>
     <t>CP-RNF-010</t>
+  </si>
+  <si>
+    <t>El sistema bloquea la acción y retorna mensaje de error impidiendo la cancelación</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1RwhpIx-Ea-NQUAMMZ9ep5QRj2n6CYSlh/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>No cumple con bloquear el cambio de estado</t>
+  </si>
+  <si>
+    <t>RNF-011 Precision numerica de precios</t>
   </si>
   <si>
     <t>CP-RNF-011</t>
   </si>
   <si>
+    <t>El sistema muestra el formato correcto de precio</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1cp8sSYFCroSKiOyWMDxDI1Dbxk-tnXnO/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Cumple con los decimales</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>RNF-012 Acceso publico al catalogo sin autentificacion</t>
+  </si>
+  <si>
     <t>CP-RNF-012</t>
+  </si>
+  <si>
+    <t>El sistema muestra el catalogo sin autentifiacion</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1I-vbF3-nPiXRgl2DG9Jqspa1l26rps5w/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Cumple con el catalogo publico</t>
+  </si>
+  <si>
+    <t>RNF-013 Almacenamiento de imagenes mediante URL</t>
   </si>
   <si>
     <t>CP-RNF-013</t>
   </si>
   <si>
+    <t>El sistema muestra la imagen asociada</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1TiIOSmFT9dpqgoisKLvKtOGp5NDm21PG/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Cumple con la muestra de la imagen</t>
+  </si>
+  <si>
+    <t>RNF-014 Indexacion para consultas de catalogo</t>
+  </si>
+  <si>
     <t>CP-RNF-014</t>
+  </si>
+  <si>
+    <t>El sistema filtra los productos</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1c1rZfc2RRk2xTuiFpDB17sUUVXvSoWMR/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Cumple con el filtrado</t>
+  </si>
+  <si>
+    <t>RNF-015 Propiedad y Control de Modificación de Notificaciones</t>
   </si>
   <si>
     <t>CP-RNF-015</t>
   </si>
   <si>
+    <t>El sistema marca las notificaciones como leidas o no leidas</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hjiSBhFQ5__h0ZmpUTG6CvA4YMDkCTbH/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Cumple con el cambio de estado</t>
+  </si>
+  <si>
+    <t>RNF-016 Formato de fechas</t>
+  </si>
+  <si>
     <t>CP-RNF-016</t>
+  </si>
+  <si>
+    <t>El sistema muestra el formato correcto de fecha</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/107Xb0qTAgce4VcCFhcluXNbjJ1-aXWYQ/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Cumple con el formato</t>
+  </si>
+  <si>
+    <t>RNF-017 Compatibilidad de nombres de propiedades</t>
   </si>
   <si>
     <t>CP-RNF-017</t>
   </si>
   <si>
+    <t>Los JSON son compatibles entre si en la API</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1-wvixIuA24RNCkZ3DzPf1zistrpYjl85/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Cumple con el funcionamiento y compatibilidad</t>
+  </si>
+  <si>
+    <t>RNF-018 Precision temporal en mensajeria</t>
+  </si>
+  <si>
     <t>CP-RNF-018</t>
   </si>
   <si>
+    <t>El sistema muestra la fecha en los mensajes</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1CV9LZE9JfkFADU36yPfu5eBZiShbda0F/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Cumple con la fecha en el chat</t>
+  </si>
+  <si>
+    <t>RNF-019 Eliminacion en cascada de mensajes de chat</t>
+  </si>
+  <si>
     <t>CP-RNF-019</t>
+  </si>
+  <si>
+    <t>El sistema borra el chat y sus mensajes relacionados</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1-yo_LOASkHOKcncEC-aqsU1v8ZI6XY4j/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Cumple con el corrado de los mensajes junto al chat</t>
   </si>
   <si>
     <t>CP-RNF-020</t>
@@ -383,19 +521,70 @@
     <t>CP-RNF-021</t>
   </si>
   <si>
+    <t>RNF-022 Almacenamiento local de sesion</t>
+  </si>
+  <si>
     <t>CP-RNF-022</t>
+  </si>
+  <si>
+    <t>El sistema guarda el token de la sesion de manera local</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Kmio_YBj-rDLy5hJWaiOysTD5n9jGWgB/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Cumple con el guardado del token</t>
   </si>
   <si>
     <t>CP-RNF-023</t>
   </si>
   <si>
+    <t>RNF-024 Estilo Visual e Identidad Corporativa</t>
+  </si>
+  <si>
     <t>CP-RNF-024</t>
+  </si>
+  <si>
+    <t>El sistema usa los colores requeridos</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1wE3HkrMBNoMChJp1n09CVKMGlrZsleud/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Cumple con el uso de los colores</t>
+  </si>
+  <si>
+    <t>RNF-025 Diseño de Interfaz Intuitivo y Autoexplicativo</t>
   </si>
   <si>
     <t>CP-RNF-025</t>
   </si>
   <si>
+    <t>El sistema muestra un diseño intuitivo</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/16BUYcY7PJX-ovMD_mm6cbPJOKWmlEzpv/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Cumple con el diseño</t>
+  </si>
+  <si>
+    <t>RNF-026 Diseño Adaptable y Multi-dispositivo</t>
+  </si>
+  <si>
     <t>CP-RNF-026</t>
+  </si>
+  <si>
+    <t>El sistema se adapta a los distintos tamaños de pantalla</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12OTx8weOodijBqDlGO5QFkq0Kk-pGRLN/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Cumple con la funcionalidad en distintos tamaños de pantalla</t>
+  </si>
+  <si>
+    <t>RNF-027 Accesibilidad e Inclusión Visual</t>
   </si>
   <si>
     <t>CP-RNF-027</t>
@@ -404,7 +593,16 @@
     <t>CP-RNF-028</t>
   </si>
   <si>
+    <t>RNF-029 Notificación Automatizada por Cambio de Estado de Servicio</t>
+  </si>
+  <si>
     <t>CP-RNF-029</t>
+  </si>
+  <si>
+    <t>El sistema genera e incrementa automáticamente la notificación en el panel/badge del cliente correspondiente</t>
+  </si>
+  <si>
+    <t>No cumple con la notificacion automatica al cambiar de estado el servicio</t>
   </si>
   <si>
     <t>CP-RNF-030</t>
@@ -542,17 +740,17 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -571,6 +769,15 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -806,8 +1013,8 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="3" t="s">
+        <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>3</v>
@@ -816,10 +1023,10 @@
         <v>4</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>8</v>
@@ -831,7 +1038,7 @@
         <v>12</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
@@ -855,7 +1062,7 @@
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
@@ -885,7 +1092,7 @@
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -2405,7 +2612,7 @@
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
@@ -2569,7 +2776,7 @@
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
@@ -2599,12 +2806,22 @@
       <c r="C59" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
+      <c r="D59" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>111</v>
+      </c>
       <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
+      <c r="I59" s="9" t="s">
+        <v>112</v>
+      </c>
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
@@ -2624,17 +2841,33 @@
       <c r="Z59" s="6"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="7"/>
-      <c r="B60" s="7"/>
+      <c r="A60" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="C60" s="8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7"/>
+      <c r="D60" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>112</v>
+      </c>
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
@@ -2654,17 +2887,31 @@
       <c r="Z60" s="6"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="7"/>
-      <c r="B61" s="7"/>
+      <c r="A61" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="C61" s="8" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
+      <c r="D61" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>123</v>
+      </c>
       <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
+      <c r="I61" s="9" t="s">
+        <v>124</v>
+      </c>
       <c r="J61" s="6"/>
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
@@ -2684,17 +2931,31 @@
       <c r="Z61" s="6"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="7"/>
-      <c r="B62" s="7"/>
+      <c r="A62" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="C62" s="8" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
+      <c r="D62" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>129</v>
+      </c>
       <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
+      <c r="I62" s="9" t="s">
+        <v>31</v>
+      </c>
       <c r="J62" s="6"/>
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
@@ -2714,17 +2975,31 @@
       <c r="Z62" s="6"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="7"/>
-      <c r="B63" s="7"/>
+      <c r="A63" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="C63" s="8" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-      <c r="G63" s="7"/>
+      <c r="D63" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>134</v>
+      </c>
       <c r="H63" s="7"/>
-      <c r="I63" s="7"/>
+      <c r="I63" s="9" t="s">
+        <v>31</v>
+      </c>
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
       <c r="L63" s="6"/>
@@ -2744,17 +3019,31 @@
       <c r="Z63" s="6"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="7"/>
-      <c r="B64" s="7"/>
+      <c r="A64" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="C64" s="8" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="7"/>
+      <c r="D64" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>139</v>
+      </c>
       <c r="H64" s="7"/>
-      <c r="I64" s="7"/>
+      <c r="I64" s="9" t="s">
+        <v>124</v>
+      </c>
       <c r="J64" s="6"/>
       <c r="K64" s="6"/>
       <c r="L64" s="6"/>
@@ -2774,17 +3063,31 @@
       <c r="Z64" s="6"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7"/>
+      <c r="A65" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="C65" s="8" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="7"/>
+      <c r="D65" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>144</v>
+      </c>
       <c r="H65" s="7"/>
-      <c r="I65" s="7"/>
+      <c r="I65" s="9" t="s">
+        <v>112</v>
+      </c>
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
@@ -2804,17 +3107,31 @@
       <c r="Z65" s="6"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="7"/>
-      <c r="B66" s="7"/>
+      <c r="A66" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="C66" s="8" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="7"/>
+      <c r="D66" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>149</v>
+      </c>
       <c r="H66" s="7"/>
-      <c r="I66" s="7"/>
+      <c r="I66" s="9" t="s">
+        <v>112</v>
+      </c>
       <c r="J66" s="6"/>
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
@@ -2834,17 +3151,31 @@
       <c r="Z66" s="6"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="7"/>
-      <c r="B67" s="7"/>
+      <c r="A67" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="C67" s="8" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="7"/>
+      <c r="D67" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>154</v>
+      </c>
       <c r="H67" s="7"/>
-      <c r="I67" s="7"/>
+      <c r="I67" s="9" t="s">
+        <v>31</v>
+      </c>
       <c r="J67" s="6"/>
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
@@ -2864,17 +3195,31 @@
       <c r="Z67" s="6"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="7"/>
-      <c r="B68" s="7"/>
+      <c r="A68" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="C68" s="8" t="s">
-        <v>117</v>
+        <v>156</v>
       </c>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
+      <c r="D68" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>159</v>
+      </c>
       <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
+      <c r="I68" s="9" t="s">
+        <v>124</v>
+      </c>
       <c r="J68" s="6"/>
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
@@ -2894,17 +3239,31 @@
       <c r="Z68" s="6"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="7"/>
-      <c r="B69" s="7"/>
+      <c r="A69" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="C69" s="8" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
+      <c r="D69" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>164</v>
+      </c>
       <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
+      <c r="I69" s="9" t="s">
+        <v>112</v>
+      </c>
       <c r="J69" s="6"/>
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
@@ -2924,10 +3283,10 @@
       <c r="Z69" s="6"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="7"/>
+      <c r="A70" s="9"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8" t="s">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="D70" s="7"/>
       <c r="E70" s="7"/>
@@ -2957,7 +3316,7 @@
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="8" t="s">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
@@ -2984,17 +3343,31 @@
       <c r="Z71" s="6"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="7"/>
-      <c r="B72" s="7"/>
+      <c r="A72" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="C72" s="8" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="7"/>
+      <c r="D72" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>171</v>
+      </c>
       <c r="H72" s="7"/>
-      <c r="I72" s="7"/>
+      <c r="I72" s="9" t="s">
+        <v>31</v>
+      </c>
       <c r="J72" s="6"/>
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
@@ -3017,7 +3390,7 @@
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="8" t="s">
-        <v>122</v>
+        <v>172</v>
       </c>
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
@@ -3044,17 +3417,31 @@
       <c r="Z73" s="6"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
+      <c r="A74" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="C74" s="8" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
+      <c r="D74" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>177</v>
+      </c>
       <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
+      <c r="I74" s="9" t="s">
+        <v>124</v>
+      </c>
       <c r="J74" s="6"/>
       <c r="K74" s="6"/>
       <c r="L74" s="6"/>
@@ -3074,17 +3461,31 @@
       <c r="Z74" s="6"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="7"/>
-      <c r="B75" s="7"/>
+      <c r="A75" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="C75" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="H75" s="7"/>
+      <c r="I75" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="7"/>
       <c r="J75" s="6"/>
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
@@ -3104,17 +3505,29 @@
       <c r="Z75" s="6"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="7"/>
-      <c r="B76" s="7"/>
+      <c r="A76" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="C76" s="8" t="s">
-        <v>125</v>
+        <v>184</v>
       </c>
-      <c r="D76" s="7"/>
+      <c r="D76" s="9" t="s">
+        <v>185</v>
+      </c>
       <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
+      <c r="F76" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>187</v>
+      </c>
       <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
+      <c r="I76" s="9" t="s">
+        <v>112</v>
+      </c>
       <c r="J76" s="6"/>
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
@@ -3134,10 +3547,14 @@
       <c r="Z76" s="6"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
+      <c r="A77" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="C77" s="8" t="s">
-        <v>126</v>
+        <v>189</v>
       </c>
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
@@ -3167,7 +3584,7 @@
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="8" t="s">
-        <v>127</v>
+        <v>190</v>
       </c>
       <c r="D78" s="7"/>
       <c r="E78" s="7"/>
@@ -3194,17 +3611,31 @@
       <c r="Z78" s="6"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="7"/>
-      <c r="B79" s="7"/>
+      <c r="A79" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>93</v>
+      </c>
       <c r="C79" s="8" t="s">
-        <v>128</v>
+        <v>192</v>
       </c>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
+      <c r="D79" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>116</v>
+      </c>
       <c r="F79" s="7"/>
-      <c r="G79" s="7"/>
-      <c r="H79" s="7"/>
-      <c r="I79" s="7"/>
+      <c r="G79" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>112</v>
+      </c>
       <c r="J79" s="6"/>
       <c r="K79" s="6"/>
       <c r="L79" s="6"/>
@@ -3227,7 +3658,7 @@
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="8" t="s">
-        <v>129</v>
+        <v>195</v>
       </c>
       <c r="D80" s="7"/>
       <c r="E80" s="7"/>
@@ -3257,7 +3688,7 @@
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="8" t="s">
-        <v>130</v>
+        <v>196</v>
       </c>
       <c r="D81" s="7"/>
       <c r="E81" s="7"/>
@@ -3287,7 +3718,7 @@
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="8" t="s">
-        <v>131</v>
+        <v>197</v>
       </c>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
@@ -3317,7 +3748,7 @@
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="8" t="s">
-        <v>132</v>
+        <v>198</v>
       </c>
       <c r="D83" s="7"/>
       <c r="E83" s="7"/>
@@ -3347,7 +3778,7 @@
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="8" t="s">
-        <v>133</v>
+        <v>199</v>
       </c>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
@@ -3377,7 +3808,7 @@
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="8" t="s">
-        <v>134</v>
+        <v>200</v>
       </c>
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
@@ -3407,7 +3838,7 @@
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="8" t="s">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="D86" s="7"/>
       <c r="E86" s="7"/>
@@ -3437,7 +3868,7 @@
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="8" t="s">
-        <v>136</v>
+        <v>202</v>
       </c>
       <c r="D87" s="7"/>
       <c r="E87" s="7"/>
@@ -3467,7 +3898,7 @@
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="8" t="s">
-        <v>137</v>
+        <v>203</v>
       </c>
       <c r="D88" s="7"/>
       <c r="E88" s="7"/>
@@ -3497,7 +3928,7 @@
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="8" t="s">
-        <v>138</v>
+        <v>204</v>
       </c>
       <c r="D89" s="7"/>
       <c r="E89" s="7"/>
@@ -3527,7 +3958,7 @@
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8" t="s">
-        <v>139</v>
+        <v>205</v>
       </c>
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
@@ -3557,7 +3988,7 @@
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="8" t="s">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="D91" s="7"/>
       <c r="E91" s="7"/>
@@ -3587,7 +4018,7 @@
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="8" t="s">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
@@ -3617,7 +4048,7 @@
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
       <c r="C93" s="8" t="s">
-        <v>142</v>
+        <v>208</v>
       </c>
       <c r="D93" s="7"/>
       <c r="E93" s="7"/>
@@ -3647,7 +4078,7 @@
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="8" t="s">
-        <v>143</v>
+        <v>209</v>
       </c>
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
@@ -3677,7 +4108,7 @@
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
       <c r="C95" s="8" t="s">
-        <v>144</v>
+        <v>210</v>
       </c>
       <c r="D95" s="7"/>
       <c r="E95" s="7"/>
@@ -3707,7 +4138,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="8" t="s">
-        <v>145</v>
+        <v>211</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
@@ -3737,7 +4168,7 @@
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
       <c r="C97" s="8" t="s">
-        <v>146</v>
+        <v>212</v>
       </c>
       <c r="D97" s="7"/>
       <c r="E97" s="7"/>
@@ -3767,7 +4198,7 @@
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="8" t="s">
-        <v>147</v>
+        <v>213</v>
       </c>
       <c r="D98" s="7"/>
       <c r="E98" s="7"/>
@@ -3797,7 +4228,7 @@
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
       <c r="C99" s="8" t="s">
-        <v>148</v>
+        <v>214</v>
       </c>
       <c r="D99" s="7"/>
       <c r="E99" s="7"/>
@@ -3827,7 +4258,7 @@
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="8" t="s">
-        <v>149</v>
+        <v>215</v>
       </c>
       <c r="D100" s="7"/>
       <c r="E100" s="7"/>
@@ -3857,7 +4288,7 @@
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="8" t="s">
-        <v>150</v>
+        <v>216</v>
       </c>
       <c r="D101" s="7"/>
       <c r="E101" s="7"/>
@@ -29059,11 +29490,25 @@
   <hyperlinks>
     <hyperlink r:id="rId1" ref="F53"/>
     <hyperlink r:id="rId2" ref="F58"/>
+    <hyperlink r:id="rId3" ref="F60"/>
+    <hyperlink r:id="rId4" ref="F61"/>
+    <hyperlink r:id="rId5" ref="F62"/>
+    <hyperlink r:id="rId6" ref="F63"/>
+    <hyperlink r:id="rId7" ref="F64"/>
+    <hyperlink r:id="rId8" ref="F65"/>
+    <hyperlink r:id="rId9" ref="F66"/>
+    <hyperlink r:id="rId10" ref="F67"/>
+    <hyperlink r:id="rId11" ref="F68"/>
+    <hyperlink r:id="rId12" ref="F69"/>
+    <hyperlink r:id="rId13" ref="F72"/>
+    <hyperlink r:id="rId14" ref="F74"/>
+    <hyperlink r:id="rId15" ref="F75"/>
+    <hyperlink r:id="rId16" ref="F76"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId17"/>
 </worksheet>
 </file>
 
@@ -29087,136 +29532,136 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>2</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>16</v>
+      <c r="F3" s="2" t="s">
+        <v>28</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="G3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>21</v>
+      <c r="C4" s="2" t="s">
+        <v>33</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="D4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>24</v>
+      <c r="F4" s="2" t="s">
+        <v>35</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>25</v>
+      <c r="G4" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="5">
+      <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>26</v>
+      <c r="B5" s="2" t="s">
+        <v>20</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>14</v>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>32</v>
+      <c r="I5" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -30218,48 +30663,48 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
-        <v>1</v>
+      <c r="A1" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
+      <c r="A2" s="1" t="s">
+        <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>15</v>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>23</v>
+      <c r="B6" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
